--- a/Hoadon/HD2026/HDVao/1/3502550210_HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HD2026/HDVao/1/3502550210_HDDienTuDaCapMa.xlsx
@@ -213,7 +213,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Từ ngày 01/01/2026 đến ngày 07/01/2026</t>
+          <t>Từ ngày 01/01/2026 đến ngày 31/01/2026</t>
         </is>
       </c>
     </row>
@@ -320,37 +320,37 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C26TDM</t>
+          <t>C26THL</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>077179006741</t>
+          <t>0314170588</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH TRẦN THỊ THANH THUẬN</t>
+          <t>Công ty TNHH Một Thành Viên Dược phẩm Hoa Linh Miền Nam</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>290/1A đường Nguyễn Hữu Cảnh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>18 Nguyễn Thế Lộc, Phường Bảy Hiền, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -360,17 +360,19 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
-        </is>
-      </c>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13" t="n">
-        <v>0.0</v>
-      </c>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>2236240.0</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>178899.0</v>
+      </c>
+      <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>788420.0</v>
+        <v>2415139.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -399,37 +401,37 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C26TTD</t>
+          <t>C26TDM</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>3500370861</t>
+          <t>077179006741</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN TIẾN ĐẠT</t>
+          <t>HỘ KINH DOANH TRẦN THỊ THANH THUẬN</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Số 458 Võ Thị Sáu, Ấp Phước Lộc, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>290/1A đường Nguyễn Hữu Cảnh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -439,19 +441,17 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="K8" s="13" t="n">
-        <v>1.93322E8</v>
-      </c>
-      <c r="L8" s="13" t="n">
-        <v>1.93322E7</v>
-      </c>
-      <c r="M8" s="13"/>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>2.126542E8</v>
+        <v>788420.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -485,32 +485,32 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C26TTD</t>
+          <t>C26TAA</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3500370861</t>
+          <t>1101929209</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN TIẾN ĐẠT</t>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI XUẤT NHẬP KHẨU CHẾ BIẾN THỰC PHẨM TẤN TẤN PHÚC</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Số 458 Võ Thị Sáu, Ấp Phước Lộc, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Thửa số 114 tờ bản đồ số 27, Ấp Bình Tiền 2, Xã Đức Hòa, Tỉnh Tây Ninh.</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -524,15 +524,17 @@
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>2.36955E8</v>
+        <v>1.2314815E7</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>2.36955E7</v>
-      </c>
-      <c r="M9" s="13"/>
+        <v>985185.0</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>2.606505E8</v>
+        <v>1.33E7</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -566,32 +568,32 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C26THT</t>
+          <t>C26TTD</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3500405761</t>
+          <t>3500370861</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
+          <t>DOANH NGHIỆP TƯ NHÂN TIẾN ĐẠT</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
+          <t>Số 458 Võ Thị Sáu, Ấp Phước Lộc, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -605,17 +607,15 @@
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>4791620.0</v>
+        <v>1.93322E8</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>383330.0</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>1.93322E7</v>
+      </c>
+      <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>5174950.0</v>
+        <v>2.126542E8</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -649,32 +649,32 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C26THT</t>
+          <t>C26TTD</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3500405761</t>
+          <t>3500370861</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
+          <t>DOANH NGHIỆP TƯ NHÂN TIẾN ĐẠT</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
+          <t>Số 458 Võ Thị Sáu, Ấp Phước Lộc, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -688,17 +688,15 @@
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>4466666.0</v>
+        <v>2.36955E8</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>357334.0</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>2.36955E7</v>
+      </c>
+      <c r="M11" s="13"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>4824000.0</v>
+        <v>2.606505E8</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -737,7 +735,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>103</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -771,17 +769,17 @@
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>2638834.0</v>
+        <v>4791620.0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>211107.0</v>
+        <v>383330.0</v>
       </c>
       <c r="M12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
-        <v>2849941.0</v>
+        <v>5174950.0</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -820,7 +818,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -854,17 +852,17 @@
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>661111.0</v>
+        <v>4466666.0</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>52889.0</v>
+        <v>357334.0</v>
       </c>
       <c r="M13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>714000.0</v>
+        <v>4824000.0</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -903,12 +901,12 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>129</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -937,17 +935,17 @@
         </is>
       </c>
       <c r="K14" s="13" t="n">
-        <v>4778400.0</v>
+        <v>2638834.0</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>382272.0</v>
+        <v>211107.0</v>
       </c>
       <c r="M14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="n">
-        <v>5160672.0</v>
+        <v>2849941.0</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -986,12 +984,12 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>159</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1020,17 +1018,17 @@
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>3540278.0</v>
+        <v>661111.0</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>283222.0</v>
+        <v>52889.0</v>
       </c>
       <c r="M15" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="n">
-        <v>3823500.0</v>
+        <v>714000.0</v>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
@@ -1069,12 +1067,12 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>412</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1103,17 +1101,17 @@
         </is>
       </c>
       <c r="K16" s="13" t="n">
-        <v>1.2268518E7</v>
+        <v>8201724.0</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>981482.0</v>
+        <v>820172.0</v>
       </c>
       <c r="M16" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="n">
-        <v>1.325E7</v>
+        <v>9021896.0</v>
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
@@ -1147,32 +1145,32 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C26TKY</t>
+          <t>C26THT</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>413</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>3500410955</t>
+          <t>3500405761</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN KIM YẾN</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Số 243/1A Bình Giã, Phường Tam Thắng , Thành Phố Hồ Chí Minh</t>
+          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
@@ -1186,17 +1184,17 @@
         </is>
       </c>
       <c r="K17" s="13" t="n">
-        <v>2938852.0</v>
+        <v>1.6988889E7</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>235108.0</v>
+        <v>1359111.0</v>
       </c>
       <c r="M17" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N17" s="13"/>
       <c r="O17" s="13" t="n">
-        <v>3173960.0</v>
+        <v>1.8348E7</v>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
@@ -1210,7 +1208,7 @@
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn đã bị thay thế</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="S17" s="6" t="inlineStr">
@@ -1230,32 +1228,32 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>C26TKY</t>
+          <t>C26THT</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>3500410955</t>
+          <t>3500405761</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN KIM YẾN</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Số 243/1A Bình Giã, Phường Tam Thắng , Thành Phố Hồ Chí Minh</t>
+          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -1269,17 +1267,17 @@
         </is>
       </c>
       <c r="K18" s="13" t="n">
-        <v>2938852.0</v>
+        <v>4778400.0</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>235108.0</v>
+        <v>382272.0</v>
       </c>
       <c r="M18" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N18" s="13"/>
       <c r="O18" s="13" t="n">
-        <v>3173960.0</v>
+        <v>5160672.0</v>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
@@ -1293,7 +1291,7 @@
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn thay thế</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="S18" s="6" t="inlineStr">
@@ -1313,32 +1311,32 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>C26THM</t>
+          <t>C26THT</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>3500442139</t>
+          <t>3500405761</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Số 58/29/42 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -1352,17 +1350,17 @@
         </is>
       </c>
       <c r="K19" s="13" t="n">
-        <v>1.3611111E7</v>
+        <v>3540278.0</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>1088889.0</v>
+        <v>283222.0</v>
       </c>
       <c r="M19" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N19" s="13"/>
       <c r="O19" s="13" t="n">
-        <v>1.47E7</v>
+        <v>3823500.0</v>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
@@ -1396,12 +1394,12 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>C26TMH</t>
+          <t>C26THT</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -1411,17 +1409,17 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>3500442139</t>
+          <t>3500405761</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Số 58/29/42 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -1435,17 +1433,17 @@
         </is>
       </c>
       <c r="K20" s="13" t="n">
-        <v>9235964.0</v>
+        <v>1.2268518E7</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>738877.0</v>
+        <v>981482.0</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>1466336.0</v>
+        <v>0.0</v>
       </c>
       <c r="N20" s="13"/>
       <c r="O20" s="13" t="n">
-        <v>9974841.0</v>
+        <v>1.325E7</v>
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
@@ -1479,32 +1477,32 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>C26THM</t>
+          <t>C26TKY</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>3500636705</t>
+          <t>3500410955</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HOẠ MY</t>
+          <t>DOANH NGHIỆP TƯ NHÂN KIM YẾN</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>114 Lý Thường Kiệt, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 243/1A Bình Giã, Phường Tam Thắng , Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -1518,17 +1516,17 @@
         </is>
       </c>
       <c r="K21" s="13" t="n">
-        <v>8.7869091E7</v>
+        <v>2938852.0</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>8786909.0</v>
+        <v>235108.0</v>
       </c>
       <c r="M21" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N21" s="13"/>
       <c r="O21" s="13" t="n">
-        <v>9.6656E7</v>
+        <v>3173960.0</v>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
@@ -1542,7 +1540,7 @@
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị thay thế</t>
         </is>
       </c>
       <c r="S21" s="6" t="inlineStr">
@@ -1562,32 +1560,32 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>C26THM</t>
+          <t>C26TKY</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>3500636705</t>
+          <t>3500410955</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HOẠ MY</t>
+          <t>DOANH NGHIỆP TƯ NHÂN KIM YẾN</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>114 Lý Thường Kiệt, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 243/1A Bình Giã, Phường Tam Thắng , Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
@@ -1601,17 +1599,17 @@
         </is>
       </c>
       <c r="K22" s="13" t="n">
-        <v>1.05795455E8</v>
+        <v>2938852.0</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>1.0579545E7</v>
+        <v>235108.0</v>
       </c>
       <c r="M22" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N22" s="13"/>
       <c r="O22" s="13" t="n">
-        <v>1.16375E8</v>
+        <v>3173960.0</v>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
@@ -1625,7 +1623,7 @@
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn thay thế</t>
         </is>
       </c>
       <c r="S22" s="6" t="inlineStr">
@@ -1645,32 +1643,32 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>C26TYY</t>
+          <t>C26THM</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>165</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>3500763855</t>
+          <t>3500442139</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN THƯƠNG MẠI DỊCH VỤ HIỀN PHONG</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Số 141 đường Chu Mạnh Trinh, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 58/29/42 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -1684,17 +1682,17 @@
         </is>
       </c>
       <c r="K23" s="13" t="n">
-        <v>2250000.0</v>
+        <v>1.3611111E7</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>180000.0</v>
+        <v>1088889.0</v>
       </c>
       <c r="M23" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N23" s="13"/>
       <c r="O23" s="13" t="n">
-        <v>2430000.0</v>
+        <v>1.47E7</v>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
@@ -1728,32 +1726,32 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>C26TDH</t>
+          <t>C26THM</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>560</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>3500788257</t>
+          <t>3500442139</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ VÀ VẬN TẢI ĐÔNG HÒA PHÁT</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>158 Phan Chu Trinh, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/29/42 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
@@ -1767,17 +1765,17 @@
         </is>
       </c>
       <c r="K24" s="13" t="n">
-        <v>2.8127894E7</v>
+        <v>2278848.0</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>2250232.0</v>
+        <v>182308.0</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>6457605.0</v>
+        <v>466752.0</v>
       </c>
       <c r="N24" s="13"/>
       <c r="O24" s="13" t="n">
-        <v>3.0378126E7</v>
+        <v>2461156.0</v>
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
@@ -1811,32 +1809,32 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>C26TDH</t>
+          <t>C26THM</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>561</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>3500788257</t>
+          <t>3500442139</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ VÀ VẬN TẢI ĐÔNG HÒA PHÁT</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>158 Phan Chu Trinh, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/29/42 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
@@ -1846,21 +1844,21 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K25" s="13" t="n">
-        <v>1.9372571E7</v>
+        <v>4111688.0</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>1549806.0</v>
+        <v>328935.0</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>4617280.0</v>
+        <v>283712.0</v>
       </c>
       <c r="N25" s="13"/>
       <c r="O25" s="13" t="n">
-        <v>2.0922377E7</v>
+        <v>4440623.0</v>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
@@ -1894,32 +1892,32 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>C26THT</t>
+          <t>C26TMH</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>3500805921</t>
+          <t>3500442139</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI HÙNG TRINH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Số 8/18 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/29/42 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -1929,21 +1927,21 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K26" s="13" t="n">
-        <v>1.6747963E7</v>
+        <v>9235964.0</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>1339837.0</v>
+        <v>738877.0</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>0.0</v>
+        <v>1466336.0</v>
       </c>
       <c r="N26" s="13"/>
       <c r="O26" s="13" t="n">
-        <v>1.80878E7</v>
+        <v>9974841.0</v>
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
@@ -1977,12 +1975,12 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>C26TDL</t>
+          <t>C26THM</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -1992,17 +1990,17 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>3501970854</t>
+          <t>3500636705</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+          <t>CÔNG TY TNHH HOẠ MY</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>114 Lý Thường Kiệt, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -2016,17 +2014,17 @@
         </is>
       </c>
       <c r="K27" s="13" t="n">
-        <v>6600173.0</v>
+        <v>8.7869091E7</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>528014.0</v>
+        <v>8786909.0</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>66667.0</v>
+        <v>0.0</v>
       </c>
       <c r="N27" s="13"/>
       <c r="O27" s="13" t="n">
-        <v>7128187.0</v>
+        <v>9.6656E7</v>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
@@ -2060,32 +2058,32 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>C26TDL</t>
+          <t>C26THM</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>3501970854</t>
+          <t>3500636705</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+          <t>CÔNG TY TNHH HOẠ MY</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>114 Lý Thường Kiệt, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -2099,17 +2097,17 @@
         </is>
       </c>
       <c r="K28" s="13" t="n">
-        <v>6453981.0</v>
+        <v>1.05795455E8</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>516317.0</v>
+        <v>1.0579545E7</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>386941.0</v>
+        <v>0.0</v>
       </c>
       <c r="N28" s="13"/>
       <c r="O28" s="13" t="n">
-        <v>6970298.0</v>
+        <v>1.16375E8</v>
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
@@ -2143,32 +2141,32 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>C26TDL</t>
+          <t>C26TYY</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>3501970854</t>
+          <t>3500763855</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+          <t>DOANH NGHIỆP TƯ NHÂN THƯƠNG MẠI DỊCH VỤ HIỀN PHONG</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 141 đường Chu Mạnh Trinh, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
@@ -2182,17 +2180,17 @@
         </is>
       </c>
       <c r="K29" s="13" t="n">
-        <v>3107469.0</v>
+        <v>2250000.0</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>248599.0</v>
+        <v>180000.0</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>31481.0</v>
+        <v>0.0</v>
       </c>
       <c r="N29" s="13"/>
       <c r="O29" s="13" t="n">
-        <v>3356068.0</v>
+        <v>2430000.0</v>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
@@ -2226,32 +2224,32 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>C26TDL</t>
+          <t>C26TYY</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>3501970854</t>
+          <t>3500763855</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+          <t>DOANH NGHIỆP TƯ NHÂN THƯƠNG MẠI DỊCH VỤ HIỀN PHONG</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 141 đường Chu Mạnh Trinh, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -2265,17 +2263,17 @@
         </is>
       </c>
       <c r="K30" s="13" t="n">
-        <v>8.8763185E7</v>
+        <v>3750000.0</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>7101056.0</v>
+        <v>300000.0</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>9626659.0</v>
+        <v>0.0</v>
       </c>
       <c r="N30" s="13"/>
       <c r="O30" s="13" t="n">
-        <v>9.5864241E7</v>
+        <v>4050000.0</v>
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
@@ -2309,12 +2307,12 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>C26TDL</t>
+          <t>C26TDH</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>192</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -2324,17 +2322,17 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>3501970854</t>
+          <t>3500788257</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ VÀ VẬN TẢI ĐÔNG HÒA PHÁT</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>158 Phan Chu Trinh, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
@@ -2348,17 +2346,17 @@
         </is>
       </c>
       <c r="K31" s="13" t="n">
-        <v>470370.0</v>
+        <v>2.8127894E7</v>
       </c>
       <c r="L31" s="13" t="n">
-        <v>37630.0</v>
+        <v>2250232.0</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>29630.0</v>
+        <v>6457605.0</v>
       </c>
       <c r="N31" s="13"/>
       <c r="O31" s="13" t="n">
-        <v>508000.0</v>
+        <v>3.0378126E7</v>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
@@ -2392,32 +2390,32 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>C26TPQ</t>
+          <t>C26TDH</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>04/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>3502236614</t>
+          <t>3500788257</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN QUỐC ĐẠI - PHÚ QUÝ</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ VÀ VẬN TẢI ĐÔNG HÒA PHÁT</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Số 140/8/5A Lưu Chí Hiếu, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>158 Phan Chu Trinh, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
@@ -2427,21 +2425,21 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K32" s="13" t="n">
-        <v>7932408.0</v>
+        <v>1.9372571E7</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>634592.0</v>
+        <v>1549806.0</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>0.0</v>
+        <v>4617280.0</v>
       </c>
       <c r="N32" s="13"/>
       <c r="O32" s="13" t="n">
-        <v>8567000.0</v>
+        <v>2.0922377E7</v>
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
@@ -2475,32 +2473,32 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>C26TTT</t>
+          <t>C26THT</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>3502243033</t>
+          <t>3500805921</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI HÙNG TRINH</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 8/18 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -2510,21 +2508,21 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K33" s="13" t="n">
-        <v>4.2386111E7</v>
+        <v>1.6747963E7</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>3390889.0</v>
+        <v>1339837.0</v>
       </c>
       <c r="M33" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N33" s="13"/>
       <c r="O33" s="13" t="n">
-        <v>4.5777E7</v>
+        <v>1.80878E7</v>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
@@ -2558,32 +2556,32 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>C26TVT</t>
+          <t>C26TDL</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>3502252817</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
@@ -2593,21 +2591,21 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K34" s="13" t="n">
-        <v>1.6634259E7</v>
+        <v>6600173.0</v>
       </c>
       <c r="L34" s="13" t="n">
-        <v>1330741.0</v>
+        <v>528014.0</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>0.0</v>
+        <v>66667.0</v>
       </c>
       <c r="N34" s="13"/>
       <c r="O34" s="13" t="n">
-        <v>1.7965E7</v>
+        <v>7128187.0</v>
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
@@ -2641,12 +2639,12 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>C26TVT</t>
+          <t>C26TDL</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -2656,17 +2654,17 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>3502252817</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
@@ -2680,17 +2678,17 @@
         </is>
       </c>
       <c r="K35" s="13" t="n">
-        <v>2.4124415E7</v>
+        <v>6453981.0</v>
       </c>
       <c r="L35" s="13" t="n">
-        <v>2345035.0</v>
+        <v>516317.0</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>0.0</v>
+        <v>386941.0</v>
       </c>
       <c r="N35" s="13"/>
       <c r="O35" s="13" t="n">
-        <v>2.646945E7</v>
+        <v>6970298.0</v>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
@@ -2724,32 +2722,32 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>C26THP</t>
+          <t>C26TDL</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>3502343006</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
@@ -2763,17 +2761,17 @@
         </is>
       </c>
       <c r="K36" s="13" t="n">
-        <v>4043481.0</v>
+        <v>3107469.0</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>323479.0</v>
+        <v>248599.0</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>713548.0</v>
+        <v>31481.0</v>
       </c>
       <c r="N36" s="13"/>
       <c r="O36" s="13" t="n">
-        <v>4366960.0</v>
+        <v>3356068.0</v>
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
@@ -2807,32 +2805,32 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>C26TKN</t>
+          <t>C26TDL</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>3502380738</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KIM NGỌC KHANG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Số 06 Nguyễn Thị Minh Khai, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
@@ -2842,21 +2840,21 @@
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K37" s="13" t="n">
-        <v>1.2227273E7</v>
+        <v>345708.0</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>1222727.0</v>
+        <v>27657.0</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>0.0</v>
+        <v>10692.0</v>
       </c>
       <c r="N37" s="13"/>
       <c r="O37" s="13" t="n">
-        <v>1.345E7</v>
+        <v>373365.0</v>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
@@ -2890,32 +2888,32 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>C26TKN</t>
+          <t>C26TDL</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>3502380738</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KIM NGỌC KHANG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Số 06 Nguyễn Thị Minh Khai, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
@@ -2925,21 +2923,21 @@
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K38" s="13" t="n">
-        <v>1.2227273E7</v>
+        <v>1488960.0</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>1222727.0</v>
+        <v>119117.0</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>0.0</v>
+        <v>95040.0</v>
       </c>
       <c r="N38" s="13"/>
       <c r="O38" s="13" t="n">
-        <v>1.345E7</v>
+        <v>1608077.0</v>
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
@@ -2973,32 +2971,32 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>C26TMH</t>
+          <t>C26TDL</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>3502426816</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
@@ -3012,17 +3010,17 @@
         </is>
       </c>
       <c r="K39" s="13" t="n">
-        <v>3047305.0</v>
+        <v>180930.0</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>243784.0</v>
+        <v>14474.0</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>0.0</v>
+        <v>14670.0</v>
       </c>
       <c r="N39" s="13"/>
       <c r="O39" s="13" t="n">
-        <v>3291089.0</v>
+        <v>195404.0</v>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
@@ -3056,32 +3054,32 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>C26TMH</t>
+          <t>C26TDL</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>3502426816</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
@@ -3095,17 +3093,17 @@
         </is>
       </c>
       <c r="K40" s="13" t="n">
-        <v>1051635.0</v>
+        <v>8.8763185E7</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>84131.0</v>
+        <v>7101056.0</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>0.0</v>
+        <v>9626659.0</v>
       </c>
       <c r="N40" s="13"/>
       <c r="O40" s="13" t="n">
-        <v>1135766.0</v>
+        <v>9.5864241E7</v>
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
@@ -3139,32 +3137,32 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>C26TMQ</t>
+          <t>C26TDL</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>983</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>3502548074</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
@@ -3178,15 +3176,17 @@
         </is>
       </c>
       <c r="K41" s="13" t="n">
-        <v>5109112.0</v>
+        <v>470370.0</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>408729.0</v>
-      </c>
-      <c r="M41" s="13"/>
+        <v>37630.0</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>29630.0</v>
+      </c>
       <c r="N41" s="13"/>
       <c r="O41" s="13" t="n">
-        <v>5517841.0</v>
+        <v>508000.0</v>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
@@ -3220,32 +3220,32 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>C26TMQ</t>
+          <t>C26TPQ</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>04/01/2026</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>3502548074</t>
+          <t>3502236614</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+          <t>DOANH NGHIỆP TƯ NHÂN QUỐC ĐẠI - PHÚ QUÝ</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 140/8/5A Lưu Chí Hiếu, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
@@ -3259,15 +3259,17 @@
         </is>
       </c>
       <c r="K42" s="13" t="n">
-        <v>1602600.0</v>
+        <v>7932408.0</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>128208.0</v>
-      </c>
-      <c r="M42" s="13"/>
+        <v>634592.0</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N42" s="13"/>
       <c r="O42" s="13" t="n">
-        <v>1730808.0</v>
+        <v>8567000.0</v>
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
@@ -3301,32 +3303,32 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>C26TDD</t>
+          <t>C26TTT</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>3502548116</t>
+          <t>3502243033</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
@@ -3340,17 +3342,17 @@
         </is>
       </c>
       <c r="K43" s="13" t="n">
-        <v>1.2777778E7</v>
+        <v>4.2386111E7</v>
       </c>
       <c r="L43" s="13" t="n">
-        <v>1022222.0</v>
+        <v>3390889.0</v>
       </c>
       <c r="M43" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N43" s="13"/>
       <c r="O43" s="13" t="n">
-        <v>1.38E7</v>
+        <v>4.5777E7</v>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
@@ -3384,32 +3386,32 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>C26TDD</t>
+          <t>C26TVT</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>112</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>3502548116</t>
+          <t>3502252817</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
@@ -3419,21 +3421,21 @@
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K44" s="13" t="n">
-        <v>1.2175926E7</v>
+        <v>1.6634259E7</v>
       </c>
       <c r="L44" s="13" t="n">
-        <v>974074.0</v>
+        <v>1330741.0</v>
       </c>
       <c r="M44" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N44" s="13"/>
       <c r="O44" s="13" t="n">
-        <v>1.315E7</v>
+        <v>1.7965E7</v>
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
@@ -3467,12 +3469,12 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>C26TMD</t>
+          <t>C26TVT</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>217</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -3482,17 +3484,17 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>3502548846</t>
+          <t>3502252817</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ MD VŨNG TÀU</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>25/42/33 Nguyễn Hữu Cảnh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
@@ -3506,17 +3508,17 @@
         </is>
       </c>
       <c r="K45" s="13" t="n">
-        <v>8379648.0</v>
+        <v>2.4124415E7</v>
       </c>
       <c r="L45" s="13" t="n">
-        <v>670372.0</v>
+        <v>2345035.0</v>
       </c>
       <c r="M45" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N45" s="13"/>
       <c r="O45" s="13" t="n">
-        <v>9050020.0</v>
+        <v>2.646945E7</v>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
@@ -3550,32 +3552,32 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>C26THQ</t>
+          <t>C26THP</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>3502549416</t>
+          <t>3502343006</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TM DV HÀO QUANG LP</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>D1 Hoàng Hoa Thám, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
@@ -3585,21 +3587,21 @@
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K46" s="13" t="n">
-        <v>8775423.0</v>
+        <v>4043481.0</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>702034.0</v>
+        <v>323479.0</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>0.0</v>
+        <v>713548.0</v>
       </c>
       <c r="N46" s="13"/>
       <c r="O46" s="13" t="n">
-        <v>9477457.0</v>
+        <v>4366960.0</v>
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
@@ -3633,32 +3635,32 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>C26THP</t>
+          <t>C26TKN</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502380738</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH KIM NGỌC KHANG</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>Số 06 Nguyễn Thị Minh Khai, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -3668,21 +3670,21 @@
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
       <c r="K47" s="13" t="n">
-        <v>1.5986667E7</v>
+        <v>1.2227273E7</v>
       </c>
       <c r="L47" s="13" t="n">
-        <v>1278933.0</v>
+        <v>1222727.0</v>
       </c>
       <c r="M47" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N47" s="13"/>
       <c r="O47" s="13" t="n">
-        <v>1.72656E7</v>
+        <v>1.345E7</v>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
@@ -3716,12 +3718,12 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>C26THB</t>
+          <t>C26TKN</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>113</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
@@ -3731,17 +3733,17 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>3502552641</t>
+          <t>3502380738</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HB COFFEE</t>
+          <t>CÔNG TY TNHH KIM NGỌC KHANG</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>24 Huỳnh Văn Hớn, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 06 Nguyễn Thị Minh Khai, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -3751,38 +3753,1443 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
       <c r="K48" s="13" t="n">
-        <v>1717590.0</v>
+        <v>1.2227273E7</v>
       </c>
       <c r="L48" s="13" t="n">
-        <v>137407.0</v>
+        <v>1222727.0</v>
       </c>
       <c r="M48" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N48" s="13"/>
       <c r="O48" s="13" t="n">
+        <v>1.345E7</v>
+      </c>
+      <c r="P48" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q48" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S48" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>43.0</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>C26TMH</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>06/01/2026</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>3502426816</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="n">
+        <v>3047305.0</v>
+      </c>
+      <c r="L49" s="13" t="n">
+        <v>243784.0</v>
+      </c>
+      <c r="M49" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N49" s="13"/>
+      <c r="O49" s="13" t="n">
+        <v>3291089.0</v>
+      </c>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q49" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S49" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>C26TMH</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>06/01/2026</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>3502426816</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="n">
+        <v>1051635.0</v>
+      </c>
+      <c r="L50" s="13" t="n">
+        <v>84131.0</v>
+      </c>
+      <c r="M50" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N50" s="13"/>
+      <c r="O50" s="13" t="n">
+        <v>1135766.0</v>
+      </c>
+      <c r="P50" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q50" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S50" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>C26TMH</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>3502426816</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="n">
+        <v>1458333.0</v>
+      </c>
+      <c r="L51" s="13" t="n">
+        <v>116667.0</v>
+      </c>
+      <c r="M51" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13" t="n">
+        <v>1575000.0</v>
+      </c>
+      <c r="P51" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q51" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S51" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>C26TMH</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>3502426816</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="n">
+        <v>1.8277778E7</v>
+      </c>
+      <c r="L52" s="13" t="n">
+        <v>1462222.0</v>
+      </c>
+      <c r="M52" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N52" s="13"/>
+      <c r="O52" s="13" t="n">
+        <v>1.974E7</v>
+      </c>
+      <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q52" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S52" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>C26TMH</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>3502426816</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="n">
+        <v>2521243.0</v>
+      </c>
+      <c r="L53" s="13" t="n">
+        <v>201699.0</v>
+      </c>
+      <c r="M53" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N53" s="13"/>
+      <c r="O53" s="13" t="n">
+        <v>2722942.0</v>
+      </c>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q53" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S53" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>C26TYY</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>3502461264</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TỔNG HỢP NAM THẢO</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>Số 246 đường Hùng Vương, Phường Tam Long , Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="n">
+        <v>7272727.0</v>
+      </c>
+      <c r="L54" s="13" t="n">
+        <v>727273.0</v>
+      </c>
+      <c r="M54" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N54" s="13"/>
+      <c r="O54" s="13" t="n">
+        <v>8000000.0</v>
+      </c>
+      <c r="P54" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q54" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S54" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>C26TMQ</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>06/01/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>3502548074</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="n">
+        <v>5109112.0</v>
+      </c>
+      <c r="L55" s="13" t="n">
+        <v>408729.0</v>
+      </c>
+      <c r="M55" s="13"/>
+      <c r="N55" s="13"/>
+      <c r="O55" s="13" t="n">
+        <v>5517841.0</v>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q55" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S55" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>C26TMQ</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>06/01/2026</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>3502548074</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="n">
+        <v>1602600.0</v>
+      </c>
+      <c r="L56" s="13" t="n">
+        <v>128208.0</v>
+      </c>
+      <c r="M56" s="13"/>
+      <c r="N56" s="13"/>
+      <c r="O56" s="13" t="n">
+        <v>1730808.0</v>
+      </c>
+      <c r="P56" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q56" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S56" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>51.0</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>C26TDD</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>03/01/2026</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>3502548116</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="n">
+        <v>1.2777778E7</v>
+      </c>
+      <c r="L57" s="13" t="n">
+        <v>1022222.0</v>
+      </c>
+      <c r="M57" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N57" s="13"/>
+      <c r="O57" s="13" t="n">
+        <v>1.38E7</v>
+      </c>
+      <c r="P57" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q57" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S57" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>C26TDD</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>3502548116</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="n">
+        <v>1.2175926E7</v>
+      </c>
+      <c r="L58" s="13" t="n">
+        <v>974074.0</v>
+      </c>
+      <c r="M58" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N58" s="13"/>
+      <c r="O58" s="13" t="n">
+        <v>1.315E7</v>
+      </c>
+      <c r="P58" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q58" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S58" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>53.0</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>C26TMD</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>3502548846</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ MD VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>25/42/33 Nguyễn Hữu Cảnh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>8379648.0</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>670372.0</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N59" s="13"/>
+      <c r="O59" s="13" t="n">
+        <v>9050020.0</v>
+      </c>
+      <c r="P59" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q59" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S59" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>C26THQ</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>3502549416</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TM DV HÀO QUANG LP</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>D1 Hoàng Hoa Thám, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="n">
+        <v>8775423.0</v>
+      </c>
+      <c r="L60" s="13" t="n">
+        <v>702034.0</v>
+      </c>
+      <c r="M60" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N60" s="13"/>
+      <c r="O60" s="13" t="n">
+        <v>9477457.0</v>
+      </c>
+      <c r="P60" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q60" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S60" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>C26THP</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>03/01/2026</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="n">
+        <v>1.5986667E7</v>
+      </c>
+      <c r="L61" s="13" t="n">
+        <v>1278933.0</v>
+      </c>
+      <c r="M61" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N61" s="13"/>
+      <c r="O61" s="13" t="n">
+        <v>1.72656E7</v>
+      </c>
+      <c r="P61" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q61" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S61" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>C26THP</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>4305022.0</v>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>344402.0</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N62" s="13"/>
+      <c r="O62" s="13" t="n">
+        <v>4649424.0</v>
+      </c>
+      <c r="P62" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q62" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S62" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>57.0</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>C26THP</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>294711.0</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>23577.0</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N63" s="13"/>
+      <c r="O63" s="13" t="n">
+        <v>318288.0</v>
+      </c>
+      <c r="P63" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q63" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S63" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>C26THB</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>06/01/2026</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>3502552641</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HB COFFEE</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>24 Huỳnh Văn Hớn, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="n">
+        <v>1717590.0</v>
+      </c>
+      <c r="L64" s="13" t="n">
+        <v>137407.0</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N64" s="13"/>
+      <c r="O64" s="13" t="n">
         <v>1854997.0</v>
       </c>
-      <c r="P48" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q48" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S48" s="6" t="inlineStr">
+      <c r="P64" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q64" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S64" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>C26TBR</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>3600244645-009</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY AJINOMOTO VIỆT NAM TẠI BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Số 62R Ấp Long Sơn, Xã Long Điền, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="n">
+        <v>1.8048924E7</v>
+      </c>
+      <c r="L65" s="13" t="n">
+        <v>1443914.0</v>
+      </c>
+      <c r="M65" s="13"/>
+      <c r="N65" s="13"/>
+      <c r="O65" s="13" t="n">
+        <v>1.9492838E7</v>
+      </c>
+      <c r="P65" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q65" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S65" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HD2026/HDVao/1/3502550210_HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HD2026/HDVao/1/3502550210_HDDienTuDaCapMa.xlsx
@@ -213,7 +213,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Từ ngày 01/01/2026 đến ngày 31/01/2026</t>
+          <t>Từ ngày 01/01/2026 đến ngày 10/01/2026</t>
         </is>
       </c>
     </row>
@@ -325,32 +325,32 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C26THL</t>
+          <t>C26TDT</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>10/01/2026</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0314170588</t>
+          <t>0306340860</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Công ty TNHH Một Thành Viên Dược phẩm Hoa Linh Miền Nam</t>
+          <t>CÔNG TY TNHH BẤT ĐỘNG SẢN ĐẠI THANH BÌNH</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>18 Nguyễn Thế Lộc, Phường Bảy Hiền, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>911 - 913 - 915 - 917 Nguyễn Trãi, Phường Chợ Lớn, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -364,15 +364,17 @@
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>2236240.0</v>
+        <v>1.55463E7</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>178899.0</v>
-      </c>
-      <c r="M7" s="13"/>
+        <v>1243704.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>2415139.0</v>
+        <v>1.6790004E7</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -401,37 +403,37 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C26TDM</t>
+          <t>C26THL</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>077179006741</t>
+          <t>0314170588</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH TRẦN THỊ THANH THUẬN</t>
+          <t>Công ty TNHH Một Thành Viên Dược phẩm Hoa Linh Miền Nam</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>290/1A đường Nguyễn Hữu Cảnh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>18 Nguyễn Thế Lộc, Phường Bảy Hiền, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -441,17 +443,19 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
-        </is>
-      </c>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13" t="n">
-        <v>0.0</v>
-      </c>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>2236240.0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>178899.0</v>
+      </c>
+      <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>788420.0</v>
+        <v>2415139.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -480,37 +484,37 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C26TAA</t>
+          <t>C26TDM</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>1101929209</t>
+          <t>077179006741</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI XUẤT NHẬP KHẨU CHẾ BIẾN THỰC PHẨM TẤN TẤN PHÚC</t>
+          <t>HỘ KINH DOANH TRẦN THỊ THANH THUẬN</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Thửa số 114 tờ bản đồ số 27, Ấp Bình Tiền 2, Xã Đức Hòa, Tỉnh Tây Ninh.</t>
+          <t>290/1A đường Nguyễn Hữu Cảnh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -520,21 +524,17 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="K9" s="13" t="n">
-        <v>1.2314815E7</v>
-      </c>
-      <c r="L9" s="13" t="n">
-        <v>985185.0</v>
-      </c>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
       <c r="M9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>1.33E7</v>
+        <v>788420.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -568,32 +568,32 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C26TTD</t>
+          <t>C26TAA</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3500370861</t>
+          <t>1101929209</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN TIẾN ĐẠT</t>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI XUẤT NHẬP KHẨU CHẾ BIẾN THỰC PHẨM TẤN TẤN PHÚC</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Số 458 Võ Thị Sáu, Ấp Phước Lộc, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Thửa số 114 tờ bản đồ số 27, Ấp Bình Tiền 2, Xã Đức Hòa, Tỉnh Tây Ninh.</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -607,15 +607,17 @@
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>1.93322E8</v>
+        <v>1.2314815E7</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>1.93322E7</v>
-      </c>
-      <c r="M10" s="13"/>
+        <v>985185.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>2.126542E8</v>
+        <v>1.33E7</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -654,12 +656,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -688,15 +690,15 @@
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>2.36955E8</v>
+        <v>1.93322E8</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>2.36955E7</v>
+        <v>1.93322E7</v>
       </c>
       <c r="M11" s="13"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>2.606505E8</v>
+        <v>2.126542E8</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -730,32 +732,32 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C26THT</t>
+          <t>C26TTD</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3500405761</t>
+          <t>3500370861</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
+          <t>DOANH NGHIỆP TƯ NHÂN TIẾN ĐẠT</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
+          <t>Số 458 Võ Thị Sáu, Ấp Phước Lộc, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
@@ -769,17 +771,15 @@
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>4791620.0</v>
+        <v>2.36955E8</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>383330.0</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>2.36955E7</v>
+      </c>
+      <c r="M12" s="13"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
-        <v>5174950.0</v>
+        <v>2.606505E8</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>103</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -852,17 +852,17 @@
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>4466666.0</v>
+        <v>4791620.0</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>357334.0</v>
+        <v>383330.0</v>
       </c>
       <c r="M13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>4824000.0</v>
+        <v>5174950.0</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -935,17 +935,17 @@
         </is>
       </c>
       <c r="K14" s="13" t="n">
-        <v>2638834.0</v>
+        <v>4466666.0</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>211107.0</v>
+        <v>357334.0</v>
       </c>
       <c r="M14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="n">
-        <v>2849941.0</v>
+        <v>4824000.0</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>129</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1018,17 +1018,17 @@
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>661111.0</v>
+        <v>2638834.0</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>52889.0</v>
+        <v>211107.0</v>
       </c>
       <c r="M15" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="n">
-        <v>714000.0</v>
+        <v>2849941.0</v>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>159</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1101,17 +1101,17 @@
         </is>
       </c>
       <c r="K16" s="13" t="n">
-        <v>8201724.0</v>
+        <v>661111.0</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>820172.0</v>
+        <v>52889.0</v>
       </c>
       <c r="M16" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="n">
-        <v>9021896.0</v>
+        <v>714000.0</v>
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>412</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1184,17 +1184,17 @@
         </is>
       </c>
       <c r="K17" s="13" t="n">
-        <v>1.6988889E7</v>
+        <v>8201724.0</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>1359111.0</v>
+        <v>820172.0</v>
       </c>
       <c r="M17" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N17" s="13"/>
       <c r="O17" s="13" t="n">
-        <v>1.8348E7</v>
+        <v>9021896.0</v>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>413</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1267,17 +1267,17 @@
         </is>
       </c>
       <c r="K18" s="13" t="n">
-        <v>4778400.0</v>
+        <v>1.6988889E7</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>382272.0</v>
+        <v>1359111.0</v>
       </c>
       <c r="M18" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N18" s="13"/>
       <c r="O18" s="13" t="n">
-        <v>5160672.0</v>
+        <v>1.8348E7</v>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1350,17 +1350,17 @@
         </is>
       </c>
       <c r="K19" s="13" t="n">
-        <v>3540278.0</v>
+        <v>4778400.0</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>283222.0</v>
+        <v>382272.0</v>
       </c>
       <c r="M19" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N19" s="13"/>
       <c r="O19" s="13" t="n">
-        <v>3823500.0</v>
+        <v>5160672.0</v>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>581</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1433,17 +1433,17 @@
         </is>
       </c>
       <c r="K20" s="13" t="n">
-        <v>1.2268518E7</v>
+        <v>2420000.0</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>981482.0</v>
+        <v>193600.0</v>
       </c>
       <c r="M20" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N20" s="13"/>
       <c r="O20" s="13" t="n">
-        <v>1.325E7</v>
+        <v>2613600.0</v>
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
@@ -1477,32 +1477,32 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>C26TKY</t>
+          <t>C26THT</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>3500410955</t>
+          <t>3500405761</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN KIM YẾN</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Số 243/1A Bình Giã, Phường Tam Thắng , Thành Phố Hồ Chí Minh</t>
+          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -1516,17 +1516,17 @@
         </is>
       </c>
       <c r="K21" s="13" t="n">
-        <v>2938852.0</v>
+        <v>3540278.0</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>235108.0</v>
+        <v>283222.0</v>
       </c>
       <c r="M21" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N21" s="13"/>
       <c r="O21" s="13" t="n">
-        <v>3173960.0</v>
+        <v>3823500.0</v>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn đã bị thay thế</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="S21" s="6" t="inlineStr">
@@ -1560,32 +1560,32 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>C26TKY</t>
+          <t>C26THT</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>3500410955</t>
+          <t>3500405761</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN KIM YẾN</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Số 243/1A Bình Giã, Phường Tam Thắng , Thành Phố Hồ Chí Minh</t>
+          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
@@ -1599,17 +1599,17 @@
         </is>
       </c>
       <c r="K22" s="13" t="n">
-        <v>2938852.0</v>
+        <v>1.2268518E7</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>235108.0</v>
+        <v>981482.0</v>
       </c>
       <c r="M22" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N22" s="13"/>
       <c r="O22" s="13" t="n">
-        <v>3173960.0</v>
+        <v>1.325E7</v>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn thay thế</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="S22" s="6" t="inlineStr">
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>C26THM</t>
+          <t>C26TKY</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>3500442139</t>
+          <t>3500410955</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
+          <t>DOANH NGHIỆP TƯ NHÂN KIM YẾN</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Số 58/29/42 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 243/1A Bình Giã, Phường Tam Thắng , Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -1682,17 +1682,17 @@
         </is>
       </c>
       <c r="K23" s="13" t="n">
-        <v>1.3611111E7</v>
+        <v>2938852.0</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>1088889.0</v>
+        <v>235108.0</v>
       </c>
       <c r="M23" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N23" s="13"/>
       <c r="O23" s="13" t="n">
-        <v>1.47E7</v>
+        <v>3173960.0</v>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị thay thế</t>
         </is>
       </c>
       <c r="S23" s="6" t="inlineStr">
@@ -1726,32 +1726,32 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>C26THM</t>
+          <t>C26TKY</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>3500442139</t>
+          <t>3500410955</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
+          <t>DOANH NGHIỆP TƯ NHÂN KIM YẾN</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Số 58/29/42 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 243/1A Bình Giã, Phường Tam Thắng , Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
@@ -1765,17 +1765,17 @@
         </is>
       </c>
       <c r="K24" s="13" t="n">
-        <v>2278848.0</v>
+        <v>2938852.0</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>182308.0</v>
+        <v>235108.0</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>466752.0</v>
+        <v>0.0</v>
       </c>
       <c r="N24" s="13"/>
       <c r="O24" s="13" t="n">
-        <v>2461156.0</v>
+        <v>3173960.0</v>
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn thay thế</t>
         </is>
       </c>
       <c r="S24" s="6" t="inlineStr">
@@ -1814,12 +1814,12 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>165</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1848,17 +1848,17 @@
         </is>
       </c>
       <c r="K25" s="13" t="n">
-        <v>4111688.0</v>
+        <v>1.3611111E7</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>328935.0</v>
+        <v>1088889.0</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>283712.0</v>
+        <v>0.0</v>
       </c>
       <c r="N25" s="13"/>
       <c r="O25" s="13" t="n">
-        <v>4440623.0</v>
+        <v>1.47E7</v>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
@@ -1892,17 +1892,17 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>C26TMH</t>
+          <t>C26THM</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>560</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -1931,17 +1931,17 @@
         </is>
       </c>
       <c r="K26" s="13" t="n">
-        <v>9235964.0</v>
+        <v>2278848.0</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>738877.0</v>
+        <v>182308.0</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>1466336.0</v>
+        <v>466752.0</v>
       </c>
       <c r="N26" s="13"/>
       <c r="O26" s="13" t="n">
-        <v>9974841.0</v>
+        <v>2461156.0</v>
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
@@ -1980,27 +1980,27 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>561</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>3500636705</t>
+          <t>3500442139</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HOẠ MY</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>114 Lý Thường Kiệt, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/29/42 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -2014,17 +2014,17 @@
         </is>
       </c>
       <c r="K27" s="13" t="n">
-        <v>8.7869091E7</v>
+        <v>4111688.0</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>8786909.0</v>
+        <v>328935.0</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>0.0</v>
+        <v>283712.0</v>
       </c>
       <c r="N27" s="13"/>
       <c r="O27" s="13" t="n">
-        <v>9.6656E7</v>
+        <v>4440623.0</v>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>C26THM</t>
+          <t>C26TMH</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -2073,17 +2073,17 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>3500636705</t>
+          <t>3500442139</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HOẠ MY</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>114 Lý Thường Kiệt, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/29/42 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -2097,17 +2097,17 @@
         </is>
       </c>
       <c r="K28" s="13" t="n">
-        <v>1.05795455E8</v>
+        <v>9235964.0</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>1.0579545E7</v>
+        <v>738877.0</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>0.0</v>
+        <v>1466336.0</v>
       </c>
       <c r="N28" s="13"/>
       <c r="O28" s="13" t="n">
-        <v>1.16375E8</v>
+        <v>9974841.0</v>
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
@@ -2141,32 +2141,32 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>C26TYY</t>
+          <t>C26THM</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>3500763855</t>
+          <t>3500636705</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN THƯƠNG MẠI DỊCH VỤ HIỀN PHONG</t>
+          <t>CÔNG TY TNHH HOẠ MY</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Số 141 đường Chu Mạnh Trinh, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>114 Lý Thường Kiệt, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
@@ -2180,17 +2180,17 @@
         </is>
       </c>
       <c r="K29" s="13" t="n">
-        <v>2250000.0</v>
+        <v>8.7869091E7</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>180000.0</v>
+        <v>8786909.0</v>
       </c>
       <c r="M29" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N29" s="13"/>
       <c r="O29" s="13" t="n">
-        <v>2430000.0</v>
+        <v>9.6656E7</v>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>C26TYY</t>
+          <t>C26THM</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -2234,22 +2234,22 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>3500763855</t>
+          <t>3500636705</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN THƯƠNG MẠI DỊCH VỤ HIỀN PHONG</t>
+          <t>CÔNG TY TNHH HOẠ MY</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Số 141 đường Chu Mạnh Trinh, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>114 Lý Thường Kiệt, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -2263,17 +2263,17 @@
         </is>
       </c>
       <c r="K30" s="13" t="n">
-        <v>3750000.0</v>
+        <v>1.05795455E8</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>300000.0</v>
+        <v>1.0579545E7</v>
       </c>
       <c r="M30" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N30" s="13"/>
       <c r="O30" s="13" t="n">
-        <v>4050000.0</v>
+        <v>1.16375E8</v>
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
@@ -2307,32 +2307,32 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>C26TDH</t>
+          <t>C26TYY</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>3500788257</t>
+          <t>3500763855</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ VÀ VẬN TẢI ĐÔNG HÒA PHÁT</t>
+          <t>DOANH NGHIỆP TƯ NHÂN THƯƠNG MẠI DỊCH VỤ HIỀN PHONG</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>158 Phan Chu Trinh, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 141 đường Chu Mạnh Trinh, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
@@ -2346,17 +2346,17 @@
         </is>
       </c>
       <c r="K31" s="13" t="n">
-        <v>2.8127894E7</v>
+        <v>3750000.0</v>
       </c>
       <c r="L31" s="13" t="n">
-        <v>2250232.0</v>
+        <v>300000.0</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>6457605.0</v>
+        <v>0.0</v>
       </c>
       <c r="N31" s="13"/>
       <c r="O31" s="13" t="n">
-        <v>3.0378126E7</v>
+        <v>4050000.0</v>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
@@ -2390,32 +2390,32 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>C26TDH</t>
+          <t>C26TYY</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>3500788257</t>
+          <t>3500763855</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ VÀ VẬN TẢI ĐÔNG HÒA PHÁT</t>
+          <t>DOANH NGHIỆP TƯ NHÂN THƯƠNG MẠI DỊCH VỤ HIỀN PHONG</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>158 Phan Chu Trinh, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 141 đường Chu Mạnh Trinh, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
@@ -2425,21 +2425,21 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K32" s="13" t="n">
-        <v>1.9372571E7</v>
+        <v>2250000.0</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>1549806.0</v>
+        <v>180000.0</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>4617280.0</v>
+        <v>0.0</v>
       </c>
       <c r="N32" s="13"/>
       <c r="O32" s="13" t="n">
-        <v>2.0922377E7</v>
+        <v>2430000.0</v>
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
@@ -2473,32 +2473,32 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>C26THT</t>
+          <t>C26TYY</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>3500805921</t>
+          <t>3500763855</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI HÙNG TRINH</t>
+          <t>DOANH NGHIỆP TƯ NHÂN THƯƠNG MẠI DỊCH VỤ HIỀN PHONG</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Số 8/18 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 141 đường Chu Mạnh Trinh, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -2508,21 +2508,21 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K33" s="13" t="n">
-        <v>1.6747963E7</v>
+        <v>3750000.0</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>1339837.0</v>
+        <v>300000.0</v>
       </c>
       <c r="M33" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N33" s="13"/>
       <c r="O33" s="13" t="n">
-        <v>1.80878E7</v>
+        <v>4050000.0</v>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>C26TDL</t>
+          <t>C26TDH</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>192</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -2571,17 +2571,17 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>3501970854</t>
+          <t>3500788257</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ VÀ VẬN TẢI ĐÔNG HÒA PHÁT</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>158 Phan Chu Trinh, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
@@ -2595,17 +2595,17 @@
         </is>
       </c>
       <c r="K34" s="13" t="n">
-        <v>6600173.0</v>
+        <v>2.8127894E7</v>
       </c>
       <c r="L34" s="13" t="n">
-        <v>528014.0</v>
+        <v>2250232.0</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>66667.0</v>
+        <v>6457605.0</v>
       </c>
       <c r="N34" s="13"/>
       <c r="O34" s="13" t="n">
-        <v>7128187.0</v>
+        <v>3.0378126E7</v>
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
@@ -2639,32 +2639,32 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>C26TDL</t>
+          <t>C26TDH</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>3501970854</t>
+          <t>3500788257</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ VÀ VẬN TẢI ĐÔNG HÒA PHÁT</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>158 Phan Chu Trinh, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
@@ -2674,21 +2674,21 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K35" s="13" t="n">
-        <v>6453981.0</v>
+        <v>1.9372571E7</v>
       </c>
       <c r="L35" s="13" t="n">
-        <v>516317.0</v>
+        <v>1549806.0</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>386941.0</v>
+        <v>4617280.0</v>
       </c>
       <c r="N35" s="13"/>
       <c r="O35" s="13" t="n">
-        <v>6970298.0</v>
+        <v>2.0922377E7</v>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
@@ -2722,32 +2722,32 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>C26TDL</t>
+          <t>C26THT</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>3501970854</t>
+          <t>3500805921</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI HÙNG TRINH</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 8/18 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
@@ -2761,17 +2761,17 @@
         </is>
       </c>
       <c r="K36" s="13" t="n">
-        <v>3107469.0</v>
+        <v>3685185.0</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>248599.0</v>
+        <v>294815.0</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>31481.0</v>
+        <v>0.0</v>
       </c>
       <c r="N36" s="13"/>
       <c r="O36" s="13" t="n">
-        <v>3356068.0</v>
+        <v>3980000.0</v>
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
@@ -2805,32 +2805,32 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>C26TDL</t>
+          <t>C26THT</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>130</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>10/01/2026</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>3501970854</t>
+          <t>3500805921</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI HÙNG TRINH</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 8/18 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
@@ -2844,17 +2844,17 @@
         </is>
       </c>
       <c r="K37" s="13" t="n">
-        <v>345708.0</v>
+        <v>7416667.0</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>27657.0</v>
+        <v>593333.0</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>10692.0</v>
+        <v>0.0</v>
       </c>
       <c r="N37" s="13"/>
       <c r="O37" s="13" t="n">
-        <v>373365.0</v>
+        <v>8010000.0</v>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
@@ -2888,32 +2888,32 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>C26TDL</t>
+          <t>C26THT</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>2849</t>
+          <t>131</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>10/01/2026</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>3501970854</t>
+          <t>3500805921</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI HÙNG TRINH</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 8/18 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
@@ -2927,17 +2927,17 @@
         </is>
       </c>
       <c r="K38" s="13" t="n">
-        <v>1488960.0</v>
+        <v>2.4718519E7</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>119117.0</v>
+        <v>1977482.0</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>95040.0</v>
+        <v>0.0</v>
       </c>
       <c r="N38" s="13"/>
       <c r="O38" s="13" t="n">
-        <v>1608077.0</v>
+        <v>2.6696001E7</v>
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
@@ -2971,32 +2971,32 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>C26TDL</t>
+          <t>C26THT</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>3501970854</t>
+          <t>3500805921</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI HÙNG TRINH</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 8/18 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
@@ -3006,21 +3006,21 @@
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K39" s="13" t="n">
-        <v>180930.0</v>
+        <v>1.6747963E7</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>14474.0</v>
+        <v>1339837.0</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>14670.0</v>
+        <v>0.0</v>
       </c>
       <c r="N39" s="13"/>
       <c r="O39" s="13" t="n">
-        <v>195404.0</v>
+        <v>1.80878E7</v>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -3093,17 +3093,17 @@
         </is>
       </c>
       <c r="K40" s="13" t="n">
-        <v>8.8763185E7</v>
+        <v>6600173.0</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>7101056.0</v>
+        <v>528014.0</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>9626659.0</v>
+        <v>66667.0</v>
       </c>
       <c r="N40" s="13"/>
       <c r="O40" s="13" t="n">
-        <v>9.5864241E7</v>
+        <v>7128187.0</v>
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -3176,17 +3176,17 @@
         </is>
       </c>
       <c r="K41" s="13" t="n">
-        <v>470370.0</v>
+        <v>6453981.0</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>37630.0</v>
+        <v>516317.0</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>29630.0</v>
+        <v>386941.0</v>
       </c>
       <c r="N41" s="13"/>
       <c r="O41" s="13" t="n">
-        <v>508000.0</v>
+        <v>6970298.0</v>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
@@ -3220,32 +3220,32 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>C26TPQ</t>
+          <t>C26TDL</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>04/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>3502236614</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN QUỐC ĐẠI - PHÚ QUÝ</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Số 140/8/5A Lưu Chí Hiếu, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
@@ -3259,17 +3259,17 @@
         </is>
       </c>
       <c r="K42" s="13" t="n">
-        <v>7932408.0</v>
+        <v>3107469.0</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>634592.0</v>
+        <v>248599.0</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>0.0</v>
+        <v>31481.0</v>
       </c>
       <c r="N42" s="13"/>
       <c r="O42" s="13" t="n">
-        <v>8567000.0</v>
+        <v>3356068.0</v>
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
@@ -3303,32 +3303,32 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>C26TTT</t>
+          <t>C26TDL</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>3502243033</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
@@ -3342,17 +3342,17 @@
         </is>
       </c>
       <c r="K43" s="13" t="n">
-        <v>4.2386111E7</v>
+        <v>345708.0</v>
       </c>
       <c r="L43" s="13" t="n">
-        <v>3390889.0</v>
+        <v>27657.0</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>0.0</v>
+        <v>10692.0</v>
       </c>
       <c r="N43" s="13"/>
       <c r="O43" s="13" t="n">
-        <v>4.5777E7</v>
+        <v>373365.0</v>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
@@ -3386,32 +3386,32 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>C26TVT</t>
+          <t>C26TDL</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>3502252817</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
@@ -3421,21 +3421,21 @@
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K44" s="13" t="n">
-        <v>1.6634259E7</v>
+        <v>1488960.0</v>
       </c>
       <c r="L44" s="13" t="n">
-        <v>1330741.0</v>
+        <v>119117.0</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>0.0</v>
+        <v>95040.0</v>
       </c>
       <c r="N44" s="13"/>
       <c r="O44" s="13" t="n">
-        <v>1.7965E7</v>
+        <v>1608077.0</v>
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
@@ -3469,32 +3469,32 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>C26TVT</t>
+          <t>C26TDL</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>3502252817</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
@@ -3508,17 +3508,17 @@
         </is>
       </c>
       <c r="K45" s="13" t="n">
-        <v>2.4124415E7</v>
+        <v>180930.0</v>
       </c>
       <c r="L45" s="13" t="n">
-        <v>2345035.0</v>
+        <v>14474.0</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>0.0</v>
+        <v>14670.0</v>
       </c>
       <c r="N45" s="13"/>
       <c r="O45" s="13" t="n">
-        <v>2.646945E7</v>
+        <v>195404.0</v>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
@@ -3552,32 +3552,32 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>C26THP</t>
+          <t>C26TDL</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>3502343006</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
@@ -3591,17 +3591,17 @@
         </is>
       </c>
       <c r="K46" s="13" t="n">
-        <v>4043481.0</v>
+        <v>3342593.0</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>323479.0</v>
+        <v>267407.0</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>713548.0</v>
+        <v>0.0</v>
       </c>
       <c r="N46" s="13"/>
       <c r="O46" s="13" t="n">
-        <v>4366960.0</v>
+        <v>3610000.0</v>
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
@@ -3635,32 +3635,32 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>C26TKN</t>
+          <t>C26TDL</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>3502380738</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KIM NGỌC KHANG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Số 06 Nguyễn Thị Minh Khai, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -3670,21 +3670,21 @@
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K47" s="13" t="n">
-        <v>1.2227273E7</v>
+        <v>1972728.0</v>
       </c>
       <c r="L47" s="13" t="n">
-        <v>1222727.0</v>
+        <v>197272.0</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>0.0</v>
+        <v>68181.0</v>
       </c>
       <c r="N47" s="13"/>
       <c r="O47" s="13" t="n">
-        <v>1.345E7</v>
+        <v>2170000.0</v>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
@@ -3718,32 +3718,32 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>C26TKN</t>
+          <t>C26TDL</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>3502380738</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KIM NGỌC KHANG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Số 06 Nguyễn Thị Minh Khai, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -3753,21 +3753,21 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K48" s="13" t="n">
-        <v>1.2227273E7</v>
+        <v>3.1215927E7</v>
       </c>
       <c r="L48" s="13" t="n">
-        <v>1222727.0</v>
+        <v>2497272.0</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>0.0</v>
+        <v>2873313.0</v>
       </c>
       <c r="N48" s="13"/>
       <c r="O48" s="13" t="n">
-        <v>1.345E7</v>
+        <v>3.3713199E7</v>
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
@@ -3801,32 +3801,32 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>C26TMH</t>
+          <t>C26TDL</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>3502426816</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -3840,17 +3840,17 @@
         </is>
       </c>
       <c r="K49" s="13" t="n">
-        <v>3047305.0</v>
+        <v>829504.0</v>
       </c>
       <c r="L49" s="13" t="n">
-        <v>243784.0</v>
+        <v>66360.0</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>0.0</v>
+        <v>16896.0</v>
       </c>
       <c r="N49" s="13"/>
       <c r="O49" s="13" t="n">
-        <v>3291089.0</v>
+        <v>895864.0</v>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
@@ -3884,32 +3884,32 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>C26TMH</t>
+          <t>C26TDL</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>3502426816</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -3923,17 +3923,17 @@
         </is>
       </c>
       <c r="K50" s="13" t="n">
-        <v>1051635.0</v>
+        <v>8.8763185E7</v>
       </c>
       <c r="L50" s="13" t="n">
-        <v>84131.0</v>
+        <v>7101056.0</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>0.0</v>
+        <v>9626659.0</v>
       </c>
       <c r="N50" s="13"/>
       <c r="O50" s="13" t="n">
-        <v>1135766.0</v>
+        <v>9.5864241E7</v>
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
@@ -3967,32 +3967,32 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>C26TMH</t>
+          <t>C26TDL</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>983</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>3502426816</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -4006,17 +4006,17 @@
         </is>
       </c>
       <c r="K51" s="13" t="n">
-        <v>1458333.0</v>
+        <v>470370.0</v>
       </c>
       <c r="L51" s="13" t="n">
-        <v>116667.0</v>
+        <v>37630.0</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>0.0</v>
+        <v>29630.0</v>
       </c>
       <c r="N51" s="13"/>
       <c r="O51" s="13" t="n">
-        <v>1575000.0</v>
+        <v>508000.0</v>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
@@ -4050,32 +4050,32 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>C26TMH</t>
+          <t>C26THH</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>3502426816</t>
+          <t>3502203697</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HIỀN HÙNG</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>số 30 Phan Đăng Lưu, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -4089,17 +4089,17 @@
         </is>
       </c>
       <c r="K52" s="13" t="n">
-        <v>1.8277778E7</v>
+        <v>2087963.0</v>
       </c>
       <c r="L52" s="13" t="n">
-        <v>1462222.0</v>
+        <v>167037.0</v>
       </c>
       <c r="M52" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N52" s="13"/>
       <c r="O52" s="13" t="n">
-        <v>1.974E7</v>
+        <v>2255000.0</v>
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
@@ -4133,32 +4133,32 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>C26TMH</t>
+          <t>C26TPQ</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>04/01/2026</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>3502426816</t>
+          <t>3502236614</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+          <t>DOANH NGHIỆP TƯ NHÂN QUỐC ĐẠI - PHÚ QUÝ</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 140/8/5A Lưu Chí Hiếu, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -4172,17 +4172,17 @@
         </is>
       </c>
       <c r="K53" s="13" t="n">
-        <v>2521243.0</v>
+        <v>7932408.0</v>
       </c>
       <c r="L53" s="13" t="n">
-        <v>201699.0</v>
+        <v>634592.0</v>
       </c>
       <c r="M53" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N53" s="13"/>
       <c r="O53" s="13" t="n">
-        <v>2722942.0</v>
+        <v>8567000.0</v>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
@@ -4216,32 +4216,32 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>C26TYY</t>
+          <t>C26TTT</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>444</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>3502461264</t>
+          <t>3502243033</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI TỔNG HỢP NAM THẢO</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Số 246 đường Hùng Vương, Phường Tam Long , Thành Phố Hồ Chí Minh</t>
+          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -4255,17 +4255,17 @@
         </is>
       </c>
       <c r="K54" s="13" t="n">
-        <v>7272727.0</v>
+        <v>8352778.0</v>
       </c>
       <c r="L54" s="13" t="n">
-        <v>727273.0</v>
+        <v>668222.0</v>
       </c>
       <c r="M54" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N54" s="13"/>
       <c r="O54" s="13" t="n">
-        <v>8000000.0</v>
+        <v>9021000.0</v>
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
@@ -4299,32 +4299,32 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>C26TMQ</t>
+          <t>C26TTT</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>3502548074</t>
+          <t>3502243033</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
@@ -4338,15 +4338,17 @@
         </is>
       </c>
       <c r="K55" s="13" t="n">
-        <v>5109112.0</v>
+        <v>4.2386111E7</v>
       </c>
       <c r="L55" s="13" t="n">
-        <v>408729.0</v>
-      </c>
-      <c r="M55" s="13"/>
+        <v>3390889.0</v>
+      </c>
+      <c r="M55" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N55" s="13"/>
       <c r="O55" s="13" t="n">
-        <v>5517841.0</v>
+        <v>4.5777E7</v>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
@@ -4380,32 +4382,32 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>C26TMQ</t>
+          <t>C26TTL</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>92</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>3502548074</t>
+          <t>3502250601</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ THẢO LÊ</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 15 Nguyễn Kim, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
@@ -4419,15 +4421,17 @@
         </is>
       </c>
       <c r="K56" s="13" t="n">
-        <v>1602600.0</v>
+        <v>1060803.0</v>
       </c>
       <c r="L56" s="13" t="n">
-        <v>128208.0</v>
-      </c>
-      <c r="M56" s="13"/>
+        <v>84864.0</v>
+      </c>
+      <c r="M56" s="13" t="n">
+        <v>412533.0</v>
+      </c>
       <c r="N56" s="13"/>
       <c r="O56" s="13" t="n">
-        <v>1730808.0</v>
+        <v>1145667.0</v>
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
@@ -4461,12 +4465,12 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>C26TDD</t>
+          <t>C26TVT</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>112</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
@@ -4476,17 +4480,17 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>3502548116</t>
+          <t>3502252817</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
@@ -4496,21 +4500,21 @@
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K57" s="13" t="n">
-        <v>1.2777778E7</v>
+        <v>1.6634259E7</v>
       </c>
       <c r="L57" s="13" t="n">
-        <v>1022222.0</v>
+        <v>1330741.0</v>
       </c>
       <c r="M57" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N57" s="13"/>
       <c r="O57" s="13" t="n">
-        <v>1.38E7</v>
+        <v>1.7965E7</v>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
@@ -4544,12 +4548,12 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>C26TDD</t>
+          <t>C26TVT</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>217</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -4559,17 +4563,17 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>3502548116</t>
+          <t>3502252817</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
@@ -4583,17 +4587,17 @@
         </is>
       </c>
       <c r="K58" s="13" t="n">
-        <v>1.2175926E7</v>
+        <v>2.4124415E7</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>974074.0</v>
+        <v>2345035.0</v>
       </c>
       <c r="M58" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N58" s="13"/>
       <c r="O58" s="13" t="n">
-        <v>1.315E7</v>
+        <v>2.646945E7</v>
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
@@ -4627,32 +4631,32 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>C26TMD</t>
+          <t>C26TVT</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>517</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>3502548846</t>
+          <t>3502252817</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ MD VŨNG TÀU</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>25/42/33 Nguyễn Hữu Cảnh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
@@ -4666,17 +4670,17 @@
         </is>
       </c>
       <c r="K59" s="13" t="n">
-        <v>8379648.0</v>
+        <v>3.7448479E7</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>670372.0</v>
+        <v>3567070.0</v>
       </c>
       <c r="M59" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N59" s="13"/>
       <c r="O59" s="13" t="n">
-        <v>9050020.0</v>
+        <v>4.1015549E7</v>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
@@ -4710,32 +4714,32 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>C26THQ</t>
+          <t>C26THP</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>3502549416</t>
+          <t>3502343006</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TM DV HÀO QUANG LP</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>D1 Hoàng Hoa Thám, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
@@ -4745,21 +4749,21 @@
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K60" s="13" t="n">
-        <v>8775423.0</v>
+        <v>1819377.0</v>
       </c>
       <c r="L60" s="13" t="n">
-        <v>702034.0</v>
+        <v>145550.0</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>0.0</v>
+        <v>296175.0</v>
       </c>
       <c r="N60" s="13"/>
       <c r="O60" s="13" t="n">
-        <v>9477457.0</v>
+        <v>1964927.0</v>
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
@@ -4798,27 +4802,27 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502343006</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
@@ -4832,17 +4836,17 @@
         </is>
       </c>
       <c r="K61" s="13" t="n">
-        <v>1.5986667E7</v>
+        <v>1.005809E7</v>
       </c>
       <c r="L61" s="13" t="n">
-        <v>1278933.0</v>
+        <v>804649.0</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>0.0</v>
+        <v>1703505.0</v>
       </c>
       <c r="N61" s="13"/>
       <c r="O61" s="13" t="n">
-        <v>1.72656E7</v>
+        <v>1.0862739E7</v>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
@@ -4881,27 +4885,27 @@
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502343006</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
@@ -4915,17 +4919,17 @@
         </is>
       </c>
       <c r="K62" s="13" t="n">
-        <v>4305022.0</v>
+        <v>4676701.0</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>344402.0</v>
+        <v>374136.0</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>0.0</v>
+        <v>842373.0</v>
       </c>
       <c r="N62" s="13"/>
       <c r="O62" s="13" t="n">
-        <v>4649424.0</v>
+        <v>5050837.0</v>
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
@@ -4964,27 +4968,27 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502343006</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
@@ -4998,17 +5002,17 @@
         </is>
       </c>
       <c r="K63" s="13" t="n">
-        <v>294711.0</v>
+        <v>4043481.0</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>23577.0</v>
+        <v>323479.0</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>0.0</v>
+        <v>713548.0</v>
       </c>
       <c r="N63" s="13"/>
       <c r="O63" s="13" t="n">
-        <v>318288.0</v>
+        <v>4366960.0</v>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
@@ -5042,32 +5046,32 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>C26THB</t>
+          <t>C26TKN</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>3502552641</t>
+          <t>3502380738</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HB COFFEE</t>
+          <t>CÔNG TY TNHH KIM NGỌC KHANG</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>24 Huỳnh Văn Hớn, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 06 Nguyễn Thị Minh Khai, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -5077,21 +5081,21 @@
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
       <c r="K64" s="13" t="n">
-        <v>1717590.0</v>
+        <v>1.2227273E7</v>
       </c>
       <c r="L64" s="13" t="n">
-        <v>137407.0</v>
+        <v>1222727.0</v>
       </c>
       <c r="M64" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N64" s="13"/>
       <c r="O64" s="13" t="n">
-        <v>1854997.0</v>
+        <v>1.345E7</v>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
@@ -5125,32 +5129,32 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>C26TBR</t>
+          <t>C26TKN</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>113</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>3600244645-009</t>
+          <t>3502380738</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY AJINOMOTO VIỆT NAM TẠI BÀ RỊA - VŨNG TÀU</t>
+          <t>CÔNG TY TNHH KIM NGỌC KHANG</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Số 62R Ấp Long Sơn, Xã Long Điền, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 06 Nguyễn Thị Minh Khai, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -5160,36 +5164,1773 @@
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
       <c r="K65" s="13" t="n">
-        <v>1.8048924E7</v>
+        <v>1.2227273E7</v>
       </c>
       <c r="L65" s="13" t="n">
-        <v>1443914.0</v>
-      </c>
-      <c r="M65" s="13"/>
+        <v>1222727.0</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N65" s="13"/>
       <c r="O65" s="13" t="n">
+        <v>1.345E7</v>
+      </c>
+      <c r="P65" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q65" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S65" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>C26TKN</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>3502380738</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH KIM NGỌC KHANG</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>Số 06 Nguyễn Thị Minh Khai, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="n">
+        <v>2.1159091E7</v>
+      </c>
+      <c r="L66" s="13" t="n">
+        <v>2115909.0</v>
+      </c>
+      <c r="M66" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N66" s="13"/>
+      <c r="O66" s="13" t="n">
+        <v>2.3275E7</v>
+      </c>
+      <c r="P66" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q66" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R66" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S66" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>61.0</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>C26TMH</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>06/01/2026</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>3502426816</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="n">
+        <v>3047305.0</v>
+      </c>
+      <c r="L67" s="13" t="n">
+        <v>243784.0</v>
+      </c>
+      <c r="M67" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N67" s="13"/>
+      <c r="O67" s="13" t="n">
+        <v>3291089.0</v>
+      </c>
+      <c r="P67" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q67" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R67" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S67" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>62.0</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>C26TMH</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>06/01/2026</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>3502426816</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="n">
+        <v>1051635.0</v>
+      </c>
+      <c r="L68" s="13" t="n">
+        <v>84131.0</v>
+      </c>
+      <c r="M68" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N68" s="13"/>
+      <c r="O68" s="13" t="n">
+        <v>1135766.0</v>
+      </c>
+      <c r="P68" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q68" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S68" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>63.0</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>C26TMH</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>3502426816</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="n">
+        <v>1458333.0</v>
+      </c>
+      <c r="L69" s="13" t="n">
+        <v>116667.0</v>
+      </c>
+      <c r="M69" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N69" s="13"/>
+      <c r="O69" s="13" t="n">
+        <v>1575000.0</v>
+      </c>
+      <c r="P69" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q69" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S69" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>C26TMH</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>3502426816</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="n">
+        <v>1.8277778E7</v>
+      </c>
+      <c r="L70" s="13" t="n">
+        <v>1462222.0</v>
+      </c>
+      <c r="M70" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N70" s="13"/>
+      <c r="O70" s="13" t="n">
+        <v>1.974E7</v>
+      </c>
+      <c r="P70" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q70" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R70" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S70" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>65.0</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>C26TMH</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>3502426816</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="n">
+        <v>2521243.0</v>
+      </c>
+      <c r="L71" s="13" t="n">
+        <v>201699.0</v>
+      </c>
+      <c r="M71" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N71" s="13"/>
+      <c r="O71" s="13" t="n">
+        <v>2722942.0</v>
+      </c>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q71" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R71" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S71" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>66.0</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>C26TYY</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>3502461264</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TỔNG HỢP NAM THẢO</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>Số 246 đường Hùng Vương, Phường Tam Long , Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="n">
+        <v>7272727.0</v>
+      </c>
+      <c r="L72" s="13" t="n">
+        <v>727273.0</v>
+      </c>
+      <c r="M72" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N72" s="13"/>
+      <c r="O72" s="13" t="n">
+        <v>8000000.0</v>
+      </c>
+      <c r="P72" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q72" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R72" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S72" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>67.0</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>C26TTP</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>3502488428</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THÀNH PHÁT BÀ RỊA</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>13 Nguyễn Văn Cừ, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="n">
+        <v>1459111.0</v>
+      </c>
+      <c r="L73" s="13" t="n">
+        <v>116729.0</v>
+      </c>
+      <c r="M73" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N73" s="13"/>
+      <c r="O73" s="13" t="n">
+        <v>1575840.0</v>
+      </c>
+      <c r="P73" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q73" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R73" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S73" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>68.0</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>C26THN</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>3502509861</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ KINH DOANH TM DV HOÀNG NAM</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>780 đường 2 tháng 9, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="n">
+        <v>7766000.0</v>
+      </c>
+      <c r="L74" s="13" t="n">
+        <v>621280.0</v>
+      </c>
+      <c r="M74" s="13" t="n">
+        <v>78444.0</v>
+      </c>
+      <c r="N74" s="13"/>
+      <c r="O74" s="13" t="n">
+        <v>8387280.0</v>
+      </c>
+      <c r="P74" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q74" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R74" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S74" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>69.0</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>C26TMQ</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>06/01/2026</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>3502548074</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="n">
+        <v>5109112.0</v>
+      </c>
+      <c r="L75" s="13" t="n">
+        <v>408729.0</v>
+      </c>
+      <c r="M75" s="13"/>
+      <c r="N75" s="13"/>
+      <c r="O75" s="13" t="n">
+        <v>5517841.0</v>
+      </c>
+      <c r="P75" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q75" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R75" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S75" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>C26TMQ</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>06/01/2026</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>3502548074</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K76" s="13" t="n">
+        <v>1602600.0</v>
+      </c>
+      <c r="L76" s="13" t="n">
+        <v>128208.0</v>
+      </c>
+      <c r="M76" s="13"/>
+      <c r="N76" s="13"/>
+      <c r="O76" s="13" t="n">
+        <v>1730808.0</v>
+      </c>
+      <c r="P76" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q76" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R76" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S76" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>71.0</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>C26TMQ</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>3502548074</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K77" s="13" t="n">
+        <v>3223760.0</v>
+      </c>
+      <c r="L77" s="13" t="n">
+        <v>257901.0</v>
+      </c>
+      <c r="M77" s="13"/>
+      <c r="N77" s="13"/>
+      <c r="O77" s="13" t="n">
+        <v>3481661.0</v>
+      </c>
+      <c r="P77" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q77" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R77" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S77" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>72.0</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>C26TDD</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>03/01/2026</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>3502548116</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K78" s="13" t="n">
+        <v>1.2777778E7</v>
+      </c>
+      <c r="L78" s="13" t="n">
+        <v>1022222.0</v>
+      </c>
+      <c r="M78" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N78" s="13"/>
+      <c r="O78" s="13" t="n">
+        <v>1.38E7</v>
+      </c>
+      <c r="P78" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q78" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R78" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S78" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>73.0</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>C26TDD</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>3502548116</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K79" s="13" t="n">
+        <v>1.2175926E7</v>
+      </c>
+      <c r="L79" s="13" t="n">
+        <v>974074.0</v>
+      </c>
+      <c r="M79" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N79" s="13"/>
+      <c r="O79" s="13" t="n">
+        <v>1.315E7</v>
+      </c>
+      <c r="P79" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q79" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R79" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S79" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>74.0</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>C26TMD</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>3502548846</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ MD VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>25/42/33 Nguyễn Hữu Cảnh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K80" s="13" t="n">
+        <v>8379648.0</v>
+      </c>
+      <c r="L80" s="13" t="n">
+        <v>670372.0</v>
+      </c>
+      <c r="M80" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N80" s="13"/>
+      <c r="O80" s="13" t="n">
+        <v>9050020.0</v>
+      </c>
+      <c r="P80" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q80" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R80" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S80" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>75.0</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>C26THQ</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>3502549416</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TM DV HÀO QUANG LP</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>D1 Hoàng Hoa Thám, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K81" s="13" t="n">
+        <v>8775423.0</v>
+      </c>
+      <c r="L81" s="13" t="n">
+        <v>702034.0</v>
+      </c>
+      <c r="M81" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N81" s="13"/>
+      <c r="O81" s="13" t="n">
+        <v>9477457.0</v>
+      </c>
+      <c r="P81" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q81" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R81" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S81" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>76.0</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>C26THP</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>03/01/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K82" s="13" t="n">
+        <v>1.5986667E7</v>
+      </c>
+      <c r="L82" s="13" t="n">
+        <v>1278933.0</v>
+      </c>
+      <c r="M82" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N82" s="13"/>
+      <c r="O82" s="13" t="n">
+        <v>1.72656E7</v>
+      </c>
+      <c r="P82" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q82" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R82" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S82" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>77.0</v>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>C26THP</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K83" s="13" t="n">
+        <v>4305022.0</v>
+      </c>
+      <c r="L83" s="13" t="n">
+        <v>344402.0</v>
+      </c>
+      <c r="M83" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N83" s="13"/>
+      <c r="O83" s="13" t="n">
+        <v>4649424.0</v>
+      </c>
+      <c r="P83" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q83" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R83" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S83" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>78.0</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>C26THP</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K84" s="13" t="n">
+        <v>294711.0</v>
+      </c>
+      <c r="L84" s="13" t="n">
+        <v>23577.0</v>
+      </c>
+      <c r="M84" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N84" s="13"/>
+      <c r="O84" s="13" t="n">
+        <v>318288.0</v>
+      </c>
+      <c r="P84" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q84" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R84" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S84" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>79.0</v>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>C26THB</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>06/01/2026</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>3502552641</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HB COFFEE</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>24 Huỳnh Văn Hớn, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K85" s="13" t="n">
+        <v>1717590.0</v>
+      </c>
+      <c r="L85" s="13" t="n">
+        <v>137407.0</v>
+      </c>
+      <c r="M85" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N85" s="13"/>
+      <c r="O85" s="13" t="n">
+        <v>1854997.0</v>
+      </c>
+      <c r="P85" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q85" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R85" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S85" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>80.0</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>C26TBR</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>3600244645-009</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY AJINOMOTO VIỆT NAM TẠI BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>Số 62R Ấp Long Sơn, Xã Long Điền, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K86" s="13" t="n">
+        <v>1.8048924E7</v>
+      </c>
+      <c r="L86" s="13" t="n">
+        <v>1443914.0</v>
+      </c>
+      <c r="M86" s="13"/>
+      <c r="N86" s="13"/>
+      <c r="O86" s="13" t="n">
         <v>1.9492838E7</v>
       </c>
-      <c r="P65" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q65" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R65" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S65" s="6" t="inlineStr">
+      <c r="P86" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q86" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R86" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S86" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HD2026/HDVao/1/3502550210_HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HD2026/HDVao/1/3502550210_HDDienTuDaCapMa.xlsx
@@ -5046,32 +5046,32 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>C26TKN</t>
+          <t>C26THP</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>10/01/2026</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>3502380738</t>
+          <t>3502343006</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KIM NGỌC KHANG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Số 06 Nguyễn Thị Minh Khai, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -5081,21 +5081,21 @@
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K64" s="13" t="n">
-        <v>1.2227273E7</v>
+        <v>2.88E7</v>
       </c>
       <c r="L64" s="13" t="n">
-        <v>1222727.0</v>
+        <v>2304000.0</v>
       </c>
       <c r="M64" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N64" s="13"/>
       <c r="O64" s="13" t="n">
-        <v>1.345E7</v>
+        <v>3.1104E7</v>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
@@ -5134,12 +5134,12 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>113</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
@@ -5251,17 +5251,17 @@
         </is>
       </c>
       <c r="K66" s="13" t="n">
-        <v>2.1159091E7</v>
+        <v>1.2227273E7</v>
       </c>
       <c r="L66" s="13" t="n">
-        <v>2115909.0</v>
+        <v>1222727.0</v>
       </c>
       <c r="M66" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N66" s="13"/>
       <c r="O66" s="13" t="n">
-        <v>2.3275E7</v>
+        <v>1.345E7</v>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
@@ -5295,32 +5295,32 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>C26TMH</t>
+          <t>C26TKN</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>249</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>3502426816</t>
+          <t>3502380738</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+          <t>CÔNG TY TNHH KIM NGỌC KHANG</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 06 Nguyễn Thị Minh Khai, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
@@ -5330,21 +5330,21 @@
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
       <c r="K67" s="13" t="n">
-        <v>3047305.0</v>
+        <v>2.1159091E7</v>
       </c>
       <c r="L67" s="13" t="n">
-        <v>243784.0</v>
+        <v>2115909.0</v>
       </c>
       <c r="M67" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N67" s="13"/>
       <c r="O67" s="13" t="n">
-        <v>3291089.0</v>
+        <v>2.3275E7</v>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>138</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
@@ -5417,17 +5417,17 @@
         </is>
       </c>
       <c r="K68" s="13" t="n">
-        <v>1051635.0</v>
+        <v>3047305.0</v>
       </c>
       <c r="L68" s="13" t="n">
-        <v>84131.0</v>
+        <v>243784.0</v>
       </c>
       <c r="M68" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N68" s="13"/>
       <c r="O68" s="13" t="n">
-        <v>1135766.0</v>
+        <v>3291089.0</v>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
@@ -5466,12 +5466,12 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>178</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -5500,17 +5500,17 @@
         </is>
       </c>
       <c r="K69" s="13" t="n">
-        <v>1458333.0</v>
+        <v>1051635.0</v>
       </c>
       <c r="L69" s="13" t="n">
-        <v>116667.0</v>
+        <v>84131.0</v>
       </c>
       <c r="M69" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N69" s="13"/>
       <c r="O69" s="13" t="n">
-        <v>1575000.0</v>
+        <v>1135766.0</v>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>247</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -5583,17 +5583,17 @@
         </is>
       </c>
       <c r="K70" s="13" t="n">
-        <v>1.8277778E7</v>
+        <v>1458333.0</v>
       </c>
       <c r="L70" s="13" t="n">
-        <v>1462222.0</v>
+        <v>116667.0</v>
       </c>
       <c r="M70" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N70" s="13"/>
       <c r="O70" s="13" t="n">
-        <v>1.974E7</v>
+        <v>1575000.0</v>
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>261</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -5666,17 +5666,17 @@
         </is>
       </c>
       <c r="K71" s="13" t="n">
-        <v>2521243.0</v>
+        <v>1.8277778E7</v>
       </c>
       <c r="L71" s="13" t="n">
-        <v>201699.0</v>
+        <v>1462222.0</v>
       </c>
       <c r="M71" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N71" s="13"/>
       <c r="O71" s="13" t="n">
-        <v>2722942.0</v>
+        <v>1.974E7</v>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
@@ -5710,12 +5710,12 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>C26TYY</t>
+          <t>C26TMH</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>3502461264</t>
+          <t>3502426816</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI TỔNG HỢP NAM THẢO</t>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>Số 246 đường Hùng Vương, Phường Tam Long , Thành Phố Hồ Chí Minh</t>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
@@ -5749,17 +5749,17 @@
         </is>
       </c>
       <c r="K72" s="13" t="n">
-        <v>7272727.0</v>
+        <v>2521243.0</v>
       </c>
       <c r="L72" s="13" t="n">
-        <v>727273.0</v>
+        <v>201699.0</v>
       </c>
       <c r="M72" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N72" s="13"/>
       <c r="O72" s="13" t="n">
-        <v>8000000.0</v>
+        <v>2722942.0</v>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
@@ -5793,32 +5793,32 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>C26TTP</t>
+          <t>C26TTL</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>120</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>10/01/2026</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>3502488428</t>
+          <t>3502459466</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THÀNH PHÁT BÀ RỊA</t>
+          <t>CÔNG TY TNHH THUỐC LÁ VŨNG TÀU</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>13 Nguyễn Văn Cừ, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
@@ -5832,17 +5832,17 @@
         </is>
       </c>
       <c r="K73" s="13" t="n">
-        <v>1459111.0</v>
+        <v>2.2272727E7</v>
       </c>
       <c r="L73" s="13" t="n">
-        <v>116729.0</v>
+        <v>2227273.0</v>
       </c>
       <c r="M73" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N73" s="13"/>
       <c r="O73" s="13" t="n">
-        <v>1575840.0</v>
+        <v>2.45E7</v>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
@@ -5876,32 +5876,32 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>C26THN</t>
+          <t>C26TYY</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>3502509861</t>
+          <t>3502461264</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ KINH DOANH TM DV HOÀNG NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TỔNG HỢP NAM THẢO</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>780 đường 2 tháng 9, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 246 đường Hùng Vương, Phường Tam Long , Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
@@ -5915,17 +5915,17 @@
         </is>
       </c>
       <c r="K74" s="13" t="n">
-        <v>7766000.0</v>
+        <v>7272727.0</v>
       </c>
       <c r="L74" s="13" t="n">
-        <v>621280.0</v>
+        <v>727273.0</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>78444.0</v>
+        <v>0.0</v>
       </c>
       <c r="N74" s="13"/>
       <c r="O74" s="13" t="n">
-        <v>8387280.0</v>
+        <v>8000000.0</v>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
@@ -5959,32 +5959,32 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>C26TMQ</t>
+          <t>C26TTP</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>3502548074</t>
+          <t>3502488428</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+          <t>CÔNG TY TNHH THÀNH PHÁT BÀ RỊA</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>13 Nguyễn Văn Cừ, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr">
@@ -5998,15 +5998,17 @@
         </is>
       </c>
       <c r="K75" s="13" t="n">
-        <v>5109112.0</v>
+        <v>1459111.0</v>
       </c>
       <c r="L75" s="13" t="n">
-        <v>408729.0</v>
-      </c>
-      <c r="M75" s="13"/>
+        <v>116729.0</v>
+      </c>
+      <c r="M75" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N75" s="13"/>
       <c r="O75" s="13" t="n">
-        <v>5517841.0</v>
+        <v>1575840.0</v>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
@@ -6040,32 +6042,32 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>C26TMQ</t>
+          <t>C26THN</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>82</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>10/01/2026</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>3502548074</t>
+          <t>3502509861</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ KINH DOANH TM DV HOÀNG NAM</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>780 đường 2 tháng 9, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr">
@@ -6079,15 +6081,17 @@
         </is>
       </c>
       <c r="K76" s="13" t="n">
-        <v>1602600.0</v>
+        <v>7766000.0</v>
       </c>
       <c r="L76" s="13" t="n">
-        <v>128208.0</v>
-      </c>
-      <c r="M76" s="13"/>
+        <v>621280.0</v>
+      </c>
+      <c r="M76" s="13" t="n">
+        <v>78444.0</v>
+      </c>
       <c r="N76" s="13"/>
       <c r="O76" s="13" t="n">
-        <v>1730808.0</v>
+        <v>8387280.0</v>
       </c>
       <c r="P76" s="7" t="inlineStr">
         <is>
@@ -6126,12 +6130,12 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
@@ -6160,15 +6164,15 @@
         </is>
       </c>
       <c r="K77" s="13" t="n">
-        <v>3223760.0</v>
+        <v>5109112.0</v>
       </c>
       <c r="L77" s="13" t="n">
-        <v>257901.0</v>
+        <v>408729.0</v>
       </c>
       <c r="M77" s="13"/>
       <c r="N77" s="13"/>
       <c r="O77" s="13" t="n">
-        <v>3481661.0</v>
+        <v>5517841.0</v>
       </c>
       <c r="P77" s="7" t="inlineStr">
         <is>
@@ -6202,32 +6206,32 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>C26TDD</t>
+          <t>C26TMQ</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>3502548116</t>
+          <t>3502548074</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
@@ -6241,17 +6245,15 @@
         </is>
       </c>
       <c r="K78" s="13" t="n">
-        <v>1.2777778E7</v>
+        <v>1602600.0</v>
       </c>
       <c r="L78" s="13" t="n">
-        <v>1022222.0</v>
-      </c>
-      <c r="M78" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>128208.0</v>
+      </c>
+      <c r="M78" s="13"/>
       <c r="N78" s="13"/>
       <c r="O78" s="13" t="n">
-        <v>1.38E7</v>
+        <v>1730808.0</v>
       </c>
       <c r="P78" s="7" t="inlineStr">
         <is>
@@ -6285,32 +6287,32 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>C26TDD</t>
+          <t>C26TMQ</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>3502548116</t>
+          <t>3502548074</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
@@ -6324,17 +6326,15 @@
         </is>
       </c>
       <c r="K79" s="13" t="n">
-        <v>1.2175926E7</v>
+        <v>3223760.0</v>
       </c>
       <c r="L79" s="13" t="n">
-        <v>974074.0</v>
-      </c>
-      <c r="M79" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>257901.0</v>
+      </c>
+      <c r="M79" s="13"/>
       <c r="N79" s="13"/>
       <c r="O79" s="13" t="n">
-        <v>1.315E7</v>
+        <v>3481661.0</v>
       </c>
       <c r="P79" s="7" t="inlineStr">
         <is>
@@ -6368,32 +6368,32 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>C26TMD</t>
+          <t>C26TDD</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>3502548846</t>
+          <t>3502548116</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ MD VŨNG TÀU</t>
+          <t>CÔNG TY TNHH ĐỨC DẬT</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>25/42/33 Nguyễn Hữu Cảnh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
@@ -6407,17 +6407,17 @@
         </is>
       </c>
       <c r="K80" s="13" t="n">
-        <v>8379648.0</v>
+        <v>1.2777778E7</v>
       </c>
       <c r="L80" s="13" t="n">
-        <v>670372.0</v>
+        <v>1022222.0</v>
       </c>
       <c r="M80" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N80" s="13"/>
       <c r="O80" s="13" t="n">
-        <v>9050020.0</v>
+        <v>1.38E7</v>
       </c>
       <c r="P80" s="7" t="inlineStr">
         <is>
@@ -6451,12 +6451,12 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>C26THQ</t>
+          <t>C26TDD</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -6466,17 +6466,17 @@
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>3502549416</t>
+          <t>3502548116</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TM DV HÀO QUANG LP</t>
+          <t>CÔNG TY TNHH ĐỨC DẬT</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>D1 Hoàng Hoa Thám, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
@@ -6486,21 +6486,21 @@
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K81" s="13" t="n">
-        <v>8775423.0</v>
+        <v>1.2175926E7</v>
       </c>
       <c r="L81" s="13" t="n">
-        <v>702034.0</v>
+        <v>974074.0</v>
       </c>
       <c r="M81" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N81" s="13"/>
       <c r="O81" s="13" t="n">
-        <v>9477457.0</v>
+        <v>1.315E7</v>
       </c>
       <c r="P81" s="7" t="inlineStr">
         <is>
@@ -6534,32 +6534,32 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>C26THP</t>
+          <t>C26TMD</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502548846</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ MD VŨNG TÀU</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>25/42/33 Nguyễn Hữu Cảnh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr">
@@ -6573,17 +6573,17 @@
         </is>
       </c>
       <c r="K82" s="13" t="n">
-        <v>1.5986667E7</v>
+        <v>8379648.0</v>
       </c>
       <c r="L82" s="13" t="n">
-        <v>1278933.0</v>
+        <v>670372.0</v>
       </c>
       <c r="M82" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N82" s="13"/>
       <c r="O82" s="13" t="n">
-        <v>1.72656E7</v>
+        <v>9050020.0</v>
       </c>
       <c r="P82" s="7" t="inlineStr">
         <is>
@@ -6617,32 +6617,32 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>C26THP</t>
+          <t>C26THQ</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>180</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502549416</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH TM DV HÀO QUANG LP</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>D1 Hoàng Hoa Thám, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
@@ -6652,21 +6652,21 @@
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K83" s="13" t="n">
-        <v>4305022.0</v>
+        <v>8775423.0</v>
       </c>
       <c r="L83" s="13" t="n">
-        <v>344402.0</v>
+        <v>702034.0</v>
       </c>
       <c r="M83" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N83" s="13"/>
       <c r="O83" s="13" t="n">
-        <v>4649424.0</v>
+        <v>9477457.0</v>
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
@@ -6739,17 +6739,17 @@
         </is>
       </c>
       <c r="K84" s="13" t="n">
-        <v>294711.0</v>
+        <v>1.5986667E7</v>
       </c>
       <c r="L84" s="13" t="n">
-        <v>23577.0</v>
+        <v>1278933.0</v>
       </c>
       <c r="M84" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N84" s="13"/>
       <c r="O84" s="13" t="n">
-        <v>318288.0</v>
+        <v>1.72656E7</v>
       </c>
       <c r="P84" s="7" t="inlineStr">
         <is>
@@ -6783,32 +6783,32 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>C26THB</t>
+          <t>C26THP</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>434</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>3502552641</t>
+          <t>3502550066</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HB COFFEE</t>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>24 Huỳnh Văn Hớn, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
@@ -6822,17 +6822,17 @@
         </is>
       </c>
       <c r="K85" s="13" t="n">
-        <v>1717590.0</v>
+        <v>4305022.0</v>
       </c>
       <c r="L85" s="13" t="n">
-        <v>137407.0</v>
+        <v>344402.0</v>
       </c>
       <c r="M85" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N85" s="13"/>
       <c r="O85" s="13" t="n">
-        <v>1854997.0</v>
+        <v>4649424.0</v>
       </c>
       <c r="P85" s="7" t="inlineStr">
         <is>
@@ -6866,32 +6866,32 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>C26TBR</t>
+          <t>C26THP</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>435</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>3600244645-009</t>
+          <t>3502550066</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY AJINOMOTO VIỆT NAM TẠI BÀ RỊA - VŨNG TÀU</t>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
         </is>
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>Số 62R Ấp Long Sơn, Xã Long Điền, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
@@ -6905,32 +6905,198 @@
         </is>
       </c>
       <c r="K86" s="13" t="n">
-        <v>1.8048924E7</v>
+        <v>294711.0</v>
       </c>
       <c r="L86" s="13" t="n">
-        <v>1443914.0</v>
-      </c>
-      <c r="M86" s="13"/>
+        <v>23577.0</v>
+      </c>
+      <c r="M86" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N86" s="13"/>
       <c r="O86" s="13" t="n">
+        <v>318288.0</v>
+      </c>
+      <c r="P86" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q86" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R86" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S86" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>81.0</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>C26THB</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>06/01/2026</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>3502552641</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HB COFFEE</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>24 Huỳnh Văn Hớn, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K87" s="13" t="n">
+        <v>1717590.0</v>
+      </c>
+      <c r="L87" s="13" t="n">
+        <v>137407.0</v>
+      </c>
+      <c r="M87" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N87" s="13"/>
+      <c r="O87" s="13" t="n">
+        <v>1854997.0</v>
+      </c>
+      <c r="P87" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q87" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R87" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S87" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>82.0</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>C26TBR</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>3600244645-009</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY AJINOMOTO VIỆT NAM TẠI BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>Số 62R Ấp Long Sơn, Xã Long Điền, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I88" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K88" s="13" t="n">
+        <v>1.8048924E7</v>
+      </c>
+      <c r="L88" s="13" t="n">
+        <v>1443914.0</v>
+      </c>
+      <c r="M88" s="13"/>
+      <c r="N88" s="13"/>
+      <c r="O88" s="13" t="n">
         <v>1.9492838E7</v>
       </c>
-      <c r="P86" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q86" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R86" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S86" s="6" t="inlineStr">
+      <c r="P88" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q88" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R88" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S88" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>
